--- a/premise/data/additional_inventories/lci-PV-CIGS.xlsx
+++ b/premise/data/additional_inventories/lci-PV-CIGS.xlsx
@@ -1377,7 +1377,9 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Production of photovoltaic thin film laminates by thermal vaporization in vacuum. The modules produced at Würth Solar have a size of 1.2m by 0.6m. The weight is 12.6kg. The efficiency is 10.8%. The rated nominal power is about 78Wp per module.
+          <t>APPROVED CIS BYPASS-DIODE IDENTITY, issue74,2026-10-18. IEA PVPS Task12, Life Cycle Inventories and Life Cycle Assessments of Photovoltaic Systems,2020,Table27 CIS panel/laminate inventory: diode,unspecified,at plant1.44E-3kg/m2. https://iea-pvps.org/wp-content/uploads/2020/12/IEA-PVPS-LCI-report-2020.pdf . Replace the light-emitting-diode purchase by the existing ordinary silicon glass through-hole diode supply at GLO, preserving1.44g per m2 laminate, every other material quantity and module efficiency/lifetime. This is a generic ordinary-diode material/processing reference corresponding to the source unspecified diode, not a measured modern PV bypass package. Its native reference is a0.596g ICT glass diode; do not claim a particular bypass current rating,package count or certified operating temperature. Retain its real Cu,Ni,Mo,Sn,Pb and electronic-grade Si ingredients, rather than a zero-metal dummy or an LED semiconductor architecture. Exact source junction-box diode type,plating and solder/lead-free status remain unresolved. No extra junction box,complete panel or additional precious-metal charge is added. No native dataset,global diode market,runtime or YAML edits. Source materials2007/2010 remain historical; this identity correction does not modernize the entire CIS design. Existing production loss and disposal boundaries unchanged; no assumed recovery credit or primary/secondary-share change.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Production of photovoltaic thin film laminates by thermal vaporization in vacuum. The modules produced at Würth Solar have a size of 1.2m by 0.6m. The weight is 12.6kg. The efficiency is 10.8%. The rated nominal power is about 78Wp per module.
 Electricity use, materials, transport of materials, treatment of production wastes. Disposal after end of life. Process emissions not known (except Cd).
 Location:  Data from Würth Solar in Germany.
 Technology:  Production technology of thin film CIS cells with thermal vaporization in vacuum.
@@ -2471,7 +2473,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>market for light emitting diode</t>
+          <t>market for diode, glass-, for through-hole mounting</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2503,12 +2505,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>light emitting diode</t>
+          <t>diode, glass-, for through-hole mounting</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>(1,1,1,1,1,3); de Wild-Scholten (2014) Life Cycle Assessment of Photovoltaics Status 2011, Part 1 Data Collection (Table 46)</t>
+          <t>APPROVED CIS BYPASS-DIODE IDENTITY, issue74,2026-10-18. IEA PVPS Task12, Life Cycle Inventories and Life Cycle Assessments of Photovoltaic Systems,2020,Table27 CIS panel/laminate inventory: diode,unspecified,at plant1.44E-3kg/m2. https://iea-pvps.org/wp-content/uploads/2020/12/IEA-PVPS-LCI-report-2020.pdf . Replace the light-emitting-diode purchase by the existing ordinary silicon glass through-hole diode supply at GLO, preserving1.44g per m2 laminate, every other material quantity and module efficiency/lifetime. This is a generic ordinary-diode material/processing reference corresponding to the source unspecified diode, not a measured modern PV bypass package. Its native reference is a0.596g ICT glass diode; do not claim a particular bypass current rating,package count or certified operating temperature. Retain its real Cu,Ni,Mo,Sn,Pb and electronic-grade Si ingredients, rather than a zero-metal dummy or an LED semiconductor architecture. Exact source junction-box diode type,plating and solder/lead-free status remain unresolved. No extra junction box,complete panel or additional precious-metal charge is added. No native dataset,global diode market,runtime or YAML edits. Source materials2007/2010 remain historical; this identity correction does not modernize the entire CIS design. Existing production loss and disposal boundaries unchanged; no assumed recovery credit or primary/secondary-share change.</t>
         </is>
       </c>
     </row>
